--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Y2" t="n">
         <v>2.7</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="X2" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -672,37 +672,37 @@
         <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
         <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
         <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V2" t="n">
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>2.55</v>
@@ -714,16 +714,16 @@
         <v>1.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -675,13 +675,13 @@
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>4.08</v>
       </c>
       <c r="O2" t="n">
         <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
         <v>4.8</v>
@@ -696,19 +696,19 @@
         <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
         <v>2.55</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Z2" t="n">
         <v>1.53</v>
@@ -717,13 +717,13 @@
         <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AC2" t="n">
         <v>2.07</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,126 +628,255 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Wales Welsh Premier League</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Connah's Quay</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bala Town</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>45902.65625</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N3" t="n">
         <v>4.08</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O3" t="n">
         <v>2.5</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P3" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q3" t="n">
         <v>4.8</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R3" t="n">
         <v>1.52</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S3" t="n">
         <v>2.38</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T3" t="n">
         <v>3.5</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>1.27</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V3" t="n">
         <v>1.05</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W3" t="n">
         <v>1.44</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X3" t="n">
         <v>2.55</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y3" t="n">
         <v>2.35</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z3" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AB3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AC3" t="n">
         <v>2.07</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AD3" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AG2" t="n">
+      <c r="AG3" t="n">
         <v>1.36</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AH3" t="n">
         <v>1.73</v>
       </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45902.8125</v>
       </c>
     </row>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T2" t="n">
         <v>3.5</v>
       </c>
-      <c r="N2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="U2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA2" t="n">
         <v>4.5</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3</v>
-      </c>
       <c r="AB2" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,147 +736,18 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45902.65625</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>45902</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="3" t="n">
         <v>45902.8125</v>
       </c>
     </row>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.75</v>
@@ -684,7 +684,7 @@
         <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="R2" t="n">
         <v>1.5</v>
@@ -702,16 +702,16 @@
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
         <v>2.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA2" t="n">
         <v>4.5</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>2.75</v>
@@ -702,10 +702,10 @@
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Y2" t="n">
         <v>2.33</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
         <v>2.75</v>
@@ -684,7 +684,7 @@
         <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
         <v>1.5</v>
@@ -702,22 +702,22 @@
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
         <v>2.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="n">
         <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
         <v>2.15</v>
@@ -739,7 +739,7 @@
         <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,25 +669,25 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="M2" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.75</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.6</v>
+        <v>4.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
         <v>2.4</v>
@@ -702,7 +702,7 @@
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="X2" t="n">
         <v>2.5</v>
@@ -711,19 +711,19 @@
         <v>2.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
         <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AC2" t="n">
         <v>2.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>2.75</v>
@@ -702,16 +702,16 @@
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AA2" t="n">
         <v>4.5</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,126 +628,255 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Wales Welsh Premier League</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Connah's Quay</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bala Town</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>45902.65625</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L3" t="n">
         <v>1.84</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M3" t="n">
         <v>3.04</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N3" t="n">
         <v>4</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="O3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.4</v>
       </c>
-      <c r="T2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="T3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.25</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="V3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.55</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y3" t="n">
         <v>2.32</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z3" t="n">
         <v>1.54</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AB3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AC2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AC3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AG2" t="n">
+      <c r="AG3" t="n">
         <v>1.36</v>
       </c>
-      <c r="AH2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AH3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45902.8125</v>
       </c>
     </row>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
         <v>2.91</v>
@@ -831,28 +831,28 @@
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AA3" t="n">
         <v>4.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>4.03</v>
       </c>
       <c r="N2" t="n">
-        <v>4.75</v>
+        <v>5.79</v>
       </c>
       <c r="O2" t="n">
         <v>2.14</v>
@@ -708,10 +708,10 @@
         <v>3.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
         <v>3</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="M3" t="n">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>2.91</v>
@@ -831,16 +831,16 @@
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AA3" t="n">
         <v>4.5</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,49 +669,49 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
-        <v>4.03</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>5.79</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="Q2" t="n">
         <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
         <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
         <v>3.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA2" t="n">
         <v>3</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
         <v>2.91</v>
@@ -825,34 +825,34 @@
         <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
         <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
@@ -708,10 +708,10 @@
         <v>3.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AA2" t="n">
         <v>3</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>2.91</v>
@@ -813,19 +813,19 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="R3" t="n">
         <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
         <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
@@ -834,22 +834,22 @@
         <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="Y3" t="n">
         <v>2.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AA3" t="n">
         <v>4.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AD3" t="n">
         <v>1.7</v>
@@ -868,7 +868,7 @@
         <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>2.91</v>
@@ -831,16 +831,16 @@
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AA3" t="n">
         <v>4.55</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -681,31 +681,31 @@
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
         <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="X2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Y2" t="n">
         <v>1.7</v>
@@ -720,10 +720,10 @@
         <v>1.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AI2" t="n">
         <v>1.8</v>
@@ -807,28 +807,28 @@
         <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="R3" t="n">
         <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T3" t="n">
         <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
         <v>1.55</v>
@@ -843,10 +843,10 @@
         <v>1.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
         <v>2.06</v>
@@ -868,7 +868,7 @@
         <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -678,10 +678,10 @@
         <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="Q2" t="n">
         <v>4.5</v>
@@ -690,13 +690,13 @@
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="T2" t="n">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
@@ -705,25 +705,25 @@
         <v>1.27</v>
       </c>
       <c r="X2" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AI2" t="n">
         <v>1.8</v>
@@ -807,28 +807,28 @@
         <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.34</v>
+        <v>4.09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="T3" t="n">
         <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
         <v>1.55</v>
@@ -849,10 +849,10 @@
         <v>1.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>5.23</v>
       </c>
       <c r="O2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="P2" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="Q2" t="n">
         <v>4.5</v>
@@ -690,40 +690,40 @@
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.27</v>
       </c>
       <c r="X2" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AI2" t="n">
         <v>1.8</v>
@@ -798,58 +798,58 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>2.37</v>
       </c>
       <c r="M3" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
         <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD3" t="n">
         <v>1.68</v>

--- a/jogos_2025-09-02.xlsx
+++ b/jogos_2025-09-02.xlsx
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -727,12 +727,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58', '61', '64']</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -798,52 +798,52 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.13</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="T3" t="n">
         <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
         <v>1.5</v>
       </c>
       <c r="X3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>2.44</v>
-      </c>
       <c r="Z3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.09</v>
+        <v>4.95</v>
       </c>
       <c r="AB3" t="n">
         <v>1.18</v>
@@ -852,7 +852,7 @@
         <v>2.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
